--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -21,199 +21,199 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EncyclopediaEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CocruwaEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Encyclopedia</x:t>
   </x:si>
   <x:si>
+    <x:t>IreanSorin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
     <x:t>Redinin</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>Renod</x:t>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
   </x:si>
   <x:si>
     <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa026</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CocruwaEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EncyclopediaEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -287,7 +287,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -305,6 +305,15 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyBorder="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="3">
@@ -973,64 +982,65 @@
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="11.03125" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="24.80078125" customWidth="1"/>
     <x:col min="5" max="5" width="8.796875" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="8.796875" style="6" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E1" s="1"/>
-      <x:c r="F1" s="1"/>
+      <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E2" s="1"/>
-      <x:c r="F2" s="1"/>
+      <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
       <x:c r="D3" s="1"/>
       <x:c r="E3" s="1"/>
-      <x:c r="F3" s="1"/>
+      <x:c r="F3" s="7"/>
       <x:c r="G3" s="1"/>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="1"/>
-      <x:c r="F4" s="1"/>
+      <x:c r="F4" s="7"/>
       <x:c r="G4" s="1"/>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -1038,16 +1048,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E5" s="1"/>
-      <x:c r="F5" s="1"/>
+      <x:c r="F5" s="7"/>
       <x:c r="G5" s="1"/>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -1055,382 +1065,406 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>3</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E6" s="1"/>
     </x:row>
-    <x:row r="7" spans="1:4">
+    <x:row r="7" spans="1:6">
       <x:c r="A7" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:5">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F7" s="7"/>
+    </x:row>
+    <x:row r="8" spans="1:6">
       <x:c r="A8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="3"/>
-    </x:row>
-    <x:row r="9" spans="1:4">
+      <x:c r="F8" s="8"/>
+    </x:row>
+    <x:row r="9" spans="1:6">
       <x:c r="A9" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:5">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F9" s="7"/>
+    </x:row>
+    <x:row r="10" spans="1:6">
       <x:c r="A10">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>1</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:5">
+      <x:c r="F10" s="8"/>
+    </x:row>
+    <x:row r="11" spans="1:6">
       <x:c r="A11" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E11" s="1"/>
-    </x:row>
-    <x:row r="12" spans="1:5">
+      <x:c r="F11" s="7"/>
+    </x:row>
+    <x:row r="12" spans="1:6">
       <x:c r="A12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>9</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="1"/>
-    </x:row>
-    <x:row r="13" spans="1:4">
+      <x:c r="F12" s="8"/>
+    </x:row>
+    <x:row r="13" spans="1:6">
       <x:c r="A13" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:5">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F13" s="7"/>
+    </x:row>
+    <x:row r="14" spans="1:6">
       <x:c r="A14">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>6</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:4">
+      <x:c r="F14" s="8"/>
+    </x:row>
+    <x:row r="15" spans="1:6">
       <x:c r="A15" s="1">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:5">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="7"/>
+    </x:row>
+    <x:row r="16" spans="1:6">
       <x:c r="A16">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>38</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="3"/>
-    </x:row>
-    <x:row r="17" spans="1:5">
+      <x:c r="F16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:6">
       <x:c r="A17" s="1">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="1"/>
-    </x:row>
-    <x:row r="18" spans="1:5">
+      <x:c r="F17" s="7"/>
+    </x:row>
+    <x:row r="18" spans="1:6">
       <x:c r="A18">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E18" s="1"/>
-    </x:row>
-    <x:row r="19" spans="1:5">
+      <x:c r="F18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:6">
       <x:c r="A19" s="1">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E19" s="4"/>
-    </x:row>
-    <x:row r="20" spans="1:5">
+      <x:c r="F19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:6">
       <x:c r="A20">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E20" s="2"/>
-    </x:row>
-    <x:row r="21" spans="1:4">
+      <x:c r="F20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:6">
       <x:c r="A21" s="1">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:5">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F21" s="7"/>
+    </x:row>
+    <x:row r="22" spans="1:6">
       <x:c r="A22">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E22" s="2"/>
-    </x:row>
-    <x:row r="23" spans="1:5">
+      <x:c r="F22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:6">
       <x:c r="A23" s="1">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="5"/>
-    </x:row>
-    <x:row r="24" spans="1:5">
+      <x:c r="F23" s="7"/>
+    </x:row>
+    <x:row r="24" spans="1:6">
       <x:c r="A24">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>30</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E24" s="1"/>
-    </x:row>
-    <x:row r="25" spans="1:5">
+      <x:c r="F24" s="8"/>
+    </x:row>
+    <x:row r="25" spans="1:6">
       <x:c r="A25" s="1">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E25" s="4"/>
-    </x:row>
-    <x:row r="26" spans="1:5">
+      <x:c r="F25" s="7"/>
+    </x:row>
+    <x:row r="26" spans="1:6">
       <x:c r="A26">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E26" s="2"/>
-    </x:row>
-    <x:row r="27" spans="1:4">
+      <x:c r="F26" s="8"/>
+    </x:row>
+    <x:row r="27" spans="1:6">
       <x:c r="A27" s="1">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:5">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F27" s="7"/>
+    </x:row>
+    <x:row r="28" spans="1:6">
       <x:c r="A28">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D28" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E28" s="2"/>
-    </x:row>
-    <x:row r="29" spans="1:5">
+      <x:c r="F28" s="8"/>
+    </x:row>
+    <x:row r="29" spans="1:6">
       <x:c r="A29" s="1">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D29" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E29" s="5"/>
-    </x:row>
-    <x:row r="30" spans="1:5">
+      <x:c r="F29" s="7"/>
+    </x:row>
+    <x:row r="30" spans="1:6">
       <x:c r="A30">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D30" t="s">
-        <x:v>64</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E30" s="1"/>
+      <x:c r="F30" s="8"/>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
@@ -1438,13 +1472,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>13</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
@@ -1452,13 +1486,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>5</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
@@ -1466,13 +1500,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
@@ -1480,13 +1514,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
@@ -1494,13 +1528,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>8</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
@@ -1508,13 +1542,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>57</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
@@ -1522,13 +1556,13 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B38" t="s">
-        <x:v>55</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C38" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D38" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
@@ -1536,13 +1570,13 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B39" t="s">
-        <x:v>48</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C39" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
@@ -1550,13 +1584,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B40" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C40" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
@@ -1564,13 +1598,13 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B41" t="s">
-        <x:v>56</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C41" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D41" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
@@ -1578,13 +1612,13 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B42" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C42" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D42" s="2" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
@@ -1592,13 +1626,13 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B43" t="s">
-        <x:v>51</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C43" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D43" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -19,201 +19,183 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="65">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="59">
+  <x:si>
+    <x:t>GaremenTooskaDin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EncyclopediaEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GaremenTooskaDin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KaroukWingent</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IreanSorin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoutonWinner</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon_001</x:t>
+  </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>KaroukWingent_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EncyclopediaEnum</x:t>
+    <x:t>Perth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod</x:t>
+  </x:si>
+  <x:si>
+    <x:t>None</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NarosaFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perth_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Renod_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ehrlone_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrenFomos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tartaros</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BultonKajon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Redinin_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gingarsion</x:t>
   </x:si>
   <x:si>
     <x:t>CocruwaEnum</x:t>
   </x:si>
   <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_002</x:t>
-  </x:si>
-  <x:si>
     <x:t>IreanSorin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -978,7 +960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G43"/>
+  <x:dimension ref="A1:G37"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -989,16 +971,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E1" s="1"/>
       <x:c r="F1" s="7"/>
@@ -1006,16 +988,16 @@
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="1"/>
       <x:c r="F2" s="7"/>
@@ -1023,7 +1005,7 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1034,7 +1016,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1048,13 +1030,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E5" s="1"/>
       <x:c r="F5" s="7"/>
@@ -1065,13 +1047,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>57</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E6" s="1"/>
     </x:row>
@@ -1080,13 +1062,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>21</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F7" s="7"/>
     </x:row>
@@ -1095,13 +1077,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D8" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D8" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="3"/>
       <x:c r="F8" s="8"/>
@@ -1111,13 +1093,13 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F9" s="7"/>
     </x:row>
@@ -1126,13 +1108,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E10" s="3"/>
       <x:c r="F10" s="8"/>
@@ -1142,497 +1124,407 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>56</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="1"/>
       <x:c r="F11" s="7"/>
     </x:row>
     <x:row r="12" spans="1:6">
-      <x:c r="A12">
-        <x:v>8</x:v>
+      <x:c r="A12" s="1">
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="8"/>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F12" s="7"/>
     </x:row>
     <x:row r="13" spans="1:6">
       <x:c r="A13" s="1">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F13" s="7"/>
+    </x:row>
+    <x:row r="14" spans="1:6">
+      <x:c r="A14" s="1">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="7"/>
+    </x:row>
+    <x:row r="15" spans="1:6">
+      <x:c r="A15">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D15" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E15" s="1"/>
+      <x:c r="F15" s="8"/>
+    </x:row>
+    <x:row r="16" spans="1:6">
+      <x:c r="A16" s="1">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="7"/>
+    </x:row>
+    <x:row r="17" spans="1:6">
+      <x:c r="A17">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D17" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:6">
+      <x:c r="A18" s="1">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D18" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F18" s="7"/>
+    </x:row>
+    <x:row r="19" spans="1:6">
+      <x:c r="A19">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="8"/>
+    </x:row>
+    <x:row r="20" spans="1:6">
+      <x:c r="A20" s="1">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D20" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E20" s="5"/>
+      <x:c r="F20" s="7"/>
+    </x:row>
+    <x:row r="21" spans="1:6">
+      <x:c r="A21">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D21" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E21" s="1"/>
+      <x:c r="F21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:6">
+      <x:c r="A22" s="1">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D22" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="7"/>
+    </x:row>
+    <x:row r="23" spans="1:6">
+      <x:c r="A23">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D23" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="8"/>
+    </x:row>
+    <x:row r="24" spans="1:6">
+      <x:c r="A24" s="1">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D13" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F13" s="7"/>
-    </x:row>
-    <x:row r="14" spans="1:6">
-      <x:c r="A14">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D14" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E14" s="3"/>
-      <x:c r="F14" s="8"/>
-    </x:row>
-    <x:row r="15" spans="1:6">
-      <x:c r="A15" s="1">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D15" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F15" s="7"/>
-    </x:row>
-    <x:row r="16" spans="1:6">
-      <x:c r="A16">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="B24" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D24" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F24" s="7"/>
+    </x:row>
+    <x:row r="25" spans="1:6">
+      <x:c r="A25">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D25" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="8"/>
+    </x:row>
+    <x:row r="26" spans="1:6">
+      <x:c r="A26" s="1">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D26" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E26" s="5"/>
+      <x:c r="F26" s="7"/>
+    </x:row>
+    <x:row r="27" spans="1:6">
+      <x:c r="A27">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D27" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E27" s="1"/>
+      <x:c r="F27" s="8"/>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B28" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D16" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E16" s="3"/>
-      <x:c r="F16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:6">
-      <x:c r="A17" s="1">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D17" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="7"/>
-    </x:row>
-    <x:row r="18" spans="1:6">
-      <x:c r="A18">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D18" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:6">
-      <x:c r="A19" s="1">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D19" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="7"/>
-    </x:row>
-    <x:row r="20" spans="1:6">
-      <x:c r="A20">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B20" s="1" t="s">
+      <x:c r="C28" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D28" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B29" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="E20" s="2"/>
-      <x:c r="F20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:6">
-      <x:c r="A21" s="1">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D21" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F21" s="7"/>
-    </x:row>
-    <x:row r="22" spans="1:6">
-      <x:c r="A22">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D22" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E22" s="2"/>
-      <x:c r="F22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:6">
-      <x:c r="A23" s="1">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B23" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E23" s="5"/>
-      <x:c r="F23" s="7"/>
-    </x:row>
-    <x:row r="24" spans="1:6">
-      <x:c r="A24">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="8"/>
-    </x:row>
-    <x:row r="25" spans="1:6">
-      <x:c r="A25" s="1">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D25" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="7"/>
-    </x:row>
-    <x:row r="26" spans="1:6">
-      <x:c r="A26">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D26" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E26" s="2"/>
-      <x:c r="F26" s="8"/>
-    </x:row>
-    <x:row r="27" spans="1:6">
-      <x:c r="A27" s="1">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B27" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C27" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D27" t="s">
+      <x:c r="C29" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D29" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B30" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F27" s="7"/>
-    </x:row>
-    <x:row r="28" spans="1:6">
-      <x:c r="A28">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E28" s="2"/>
-      <x:c r="F28" s="8"/>
-    </x:row>
-    <x:row r="29" spans="1:6">
-      <x:c r="A29" s="1">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D29" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E29" s="5"/>
-      <x:c r="F29" s="7"/>
-    </x:row>
-    <x:row r="30" spans="1:6">
-      <x:c r="A30">
+      <x:c r="C30" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B30" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D30" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="8"/>
+      <x:c r="D30" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C31" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D31" s="2" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="C31" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D31" s="2" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>19</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>20</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>22</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>55</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>55</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>34</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>55</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B37" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C37" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D37" s="2" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B37" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C37" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D37" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:4">
-      <x:c r="A38">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B38" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C38" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D38" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:4">
-      <x:c r="A39">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B39" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C39" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D39" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:4">
-      <x:c r="A40">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B40" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C40" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D40" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:4">
-      <x:c r="A41">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B41" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C41" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D41" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:4">
-      <x:c r="A42">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B42" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C42" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D42" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:4">
-      <x:c r="A43">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B43" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C43" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D43" s="2" t="s">
-        <x:v>58</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -19,183 +19,312 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="59">
-  <x:si>
-    <x:t>GaremenTooskaDin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GaremenTooskaDin_002</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:t>EncyclopediaEnum</x:t>
   </x:si>
   <x:si>
-    <x:t>GaremenTooskaDin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KaroukWingent</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_002</x:t>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Title</x:t>
   </x:si>
   <x:si>
     <x:t>Encyclopedia</x:t>
   </x:si>
   <x:si>
-    <x:t>Gingarsion_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RoutonWinner</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod</x:t>
-  </x:si>
-  <x:si>
-    <x:t>None</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NarosaFomos</x:t>
+    <x:t>Cocruwa_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
   </x:si>
   <x:si>
     <x:t>History_004</x:t>
   </x:si>
   <x:si>
-    <x:t>Perth_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
+    <x:t>Cocruwa_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
   </x:si>
   <x:si>
     <x:t>Term_003</x:t>
   </x:si>
   <x:si>
-    <x:t>Renod_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Renod_002</x:t>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
   </x:si>
   <x:si>
     <x:t>Term_005</x:t>
   </x:si>
   <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ehrlone_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrenFomos</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tartaros</x:t>
+    <x:t>Cocruwa_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_023</x:t>
   </x:si>
   <x:si>
     <x:t>History_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BultonKajon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Redinin_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gingarsion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CocruwaEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IreanSorin</x:t>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -960,52 +1089,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:G37"/>
+  <x:dimension ref="A1:K38"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="24.80078125" customWidth="1"/>
-    <x:col min="5" max="5" width="8.796875" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="19.73828125" bestFit="1" customWidth="1"/>
     <x:col min="6" max="6" width="8.796875" style="6" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E1" s="1"/>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
       <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E2" s="1"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1016,7 +1150,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1025,507 +1159,625 @@
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="1"/>
     </x:row>
-    <x:row r="5" spans="1:7">
+    <x:row r="5" spans="1:11">
       <x:c r="A5" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E5" s="1"/>
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="1"/>
-    </x:row>
-    <x:row r="6" spans="1:5">
+      <x:c r="K5" s="1"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
       <x:c r="A6">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E6" s="1"/>
-    </x:row>
-    <x:row r="7" spans="1:6">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K6" s="1"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
       <x:c r="A7" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E7" t="s">
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F7" s="7"/>
-    </x:row>
-    <x:row r="8" spans="1:6">
+      <x:c r="K7" s="2"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
       <x:c r="A8">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E8" s="3"/>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="s">
+        <x:v>23</x:v>
+      </x:c>
       <x:c r="F8" s="8"/>
-    </x:row>
-    <x:row r="9" spans="1:6">
+      <x:c r="K8" s="3"/>
+    </x:row>
+    <x:row r="9" spans="1:11">
       <x:c r="A9" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E9" t="s">
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F9" s="7"/>
-    </x:row>
-    <x:row r="10" spans="1:6">
+      <x:c r="K9" s="2"/>
+    </x:row>
+    <x:row r="10" spans="1:11">
       <x:c r="A10">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E10" s="3"/>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
       <x:c r="F10" s="8"/>
-    </x:row>
-    <x:row r="11" spans="1:6">
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
       <x:c r="A11" s="1">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E11" s="1"/>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="F11" s="7"/>
-    </x:row>
-    <x:row r="12" spans="1:6">
+      <x:c r="K11" s="1"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
       <x:c r="A12" s="1">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>25</x:v>
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="E12" t="s">
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F12" s="7"/>
-    </x:row>
-    <x:row r="13" spans="1:6">
+      <x:c r="K12" s="2"/>
+    </x:row>
+    <x:row r="13" spans="1:11">
       <x:c r="A13" s="1">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>56</x:v>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E13" t="s">
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F13" s="7"/>
-    </x:row>
-    <x:row r="14" spans="1:6">
+      <x:c r="K13" s="2"/>
+    </x:row>
+    <x:row r="14" spans="1:11">
       <x:c r="A14" s="1">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E14" s="1"/>
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
       <x:c r="F14" s="7"/>
-    </x:row>
-    <x:row r="15" spans="1:6">
+      <x:c r="K14" s="1"/>
+    </x:row>
+    <x:row r="15" spans="1:11">
       <x:c r="A15">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E15" s="1"/>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
       <x:c r="F15" s="8"/>
-    </x:row>
-    <x:row r="16" spans="1:6">
+      <x:c r="K15" s="1"/>
+    </x:row>
+    <x:row r="16" spans="1:11">
       <x:c r="A16" s="1">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E16" s="4"/>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="F16" s="7"/>
-    </x:row>
-    <x:row r="17" spans="1:6">
+      <x:c r="K16" s="2"/>
+    </x:row>
+    <x:row r="17" spans="1:11">
       <x:c r="A17">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E17" s="2"/>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="F17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:6">
+      <x:c r="K17" s="2"/>
+    </x:row>
+    <x:row r="18" spans="1:11">
       <x:c r="A18" s="1">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>58</x:v>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E18" t="s">
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F18" s="7"/>
-    </x:row>
-    <x:row r="19" spans="1:6">
+      <x:c r="K18" s="2"/>
+    </x:row>
+    <x:row r="19" spans="1:11">
       <x:c r="A19">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D19" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E19" s="2"/>
       <x:c r="F19" s="8"/>
-    </x:row>
-    <x:row r="20" spans="1:6">
+      <x:c r="K19" s="2"/>
+    </x:row>
+    <x:row r="20" spans="1:11">
       <x:c r="A20" s="1">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E20" s="5"/>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E20" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
       <x:c r="F20" s="7"/>
-    </x:row>
-    <x:row r="21" spans="1:6">
+      <x:c r="K20" s="5"/>
+    </x:row>
+    <x:row r="21" spans="1:11">
       <x:c r="A21">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E21" s="1"/>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="F21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:6">
+      <x:c r="K21" s="1"/>
+    </x:row>
+    <x:row r="22" spans="1:11">
       <x:c r="A22" s="1">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E22" s="4"/>
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
       <x:c r="F22" s="7"/>
-    </x:row>
-    <x:row r="23" spans="1:6">
+      <x:c r="K22" s="2"/>
+    </x:row>
+    <x:row r="23" spans="1:11">
       <x:c r="A23">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E23" s="2"/>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E23" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="F23" s="8"/>
-    </x:row>
-    <x:row r="24" spans="1:6">
+      <x:c r="K23" s="2"/>
+    </x:row>
+    <x:row r="24" spans="1:11">
       <x:c r="A24" s="1">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>20</x:v>
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E24" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F24" s="7"/>
-    </x:row>
-    <x:row r="25" spans="1:6">
+      <x:c r="K24" s="2"/>
+    </x:row>
+    <x:row r="25" spans="1:11">
       <x:c r="A25">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D25" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="E25" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D25" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E25" s="2"/>
       <x:c r="F25" s="8"/>
-    </x:row>
-    <x:row r="26" spans="1:6">
+      <x:c r="K25" s="2"/>
+    </x:row>
+    <x:row r="26" spans="1:11">
       <x:c r="A26" s="1">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E26" s="5"/>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E26" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="F26" s="7"/>
-    </x:row>
-    <x:row r="27" spans="1:6">
+      <x:c r="K26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:11">
       <x:c r="A27">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E27" s="1"/>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="F27" s="8"/>
-    </x:row>
-    <x:row r="28" spans="1:4">
+      <x:c r="K27" s="1"/>
+    </x:row>
+    <x:row r="28" spans="1:11">
       <x:c r="A28">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>46</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:4">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="E28" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K28" s="2"/>
+    </x:row>
+    <x:row r="29" spans="1:11">
       <x:c r="A29">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:4">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E29" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K29" s="2"/>
+    </x:row>
+    <x:row r="30" spans="1:11">
       <x:c r="A30">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>39</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:4">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="E30" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K30" s="2"/>
+    </x:row>
+    <x:row r="31" spans="1:11">
       <x:c r="A31">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:4">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="E31" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="K31" s="2"/>
+    </x:row>
+    <x:row r="32" spans="1:11">
       <x:c r="A32">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:4">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E32" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="K32" s="2"/>
+    </x:row>
+    <x:row r="33" spans="1:11">
       <x:c r="A33">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>43</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:4">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E33" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K33" s="2"/>
+    </x:row>
+    <x:row r="34" spans="1:11">
       <x:c r="A34">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>51</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:4">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="E34" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K34" s="2"/>
+    </x:row>
+    <x:row r="35" spans="1:11">
       <x:c r="A35">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:4">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E35" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="K35" s="2"/>
+    </x:row>
+    <x:row r="36" spans="1:11">
       <x:c r="A36">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>49</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:4">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E36" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="K36" s="2"/>
+    </x:row>
+    <x:row r="37" spans="1:11">
       <x:c r="A37">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>36</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>24</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="E37" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K37" s="2"/>
+    </x:row>
+    <x:row r="38" spans="11:11">
+      <x:c r="K38" s="2"/>
     </x:row>
   </x:sheetData>
   <x:sortState columnSort="0" caseSensitive="0" ref="D6:E30">

--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -19,36 +19,207 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="102">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="107">
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EncyclopediaEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocruwa012_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
+    <x:t>Cocruwa_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa013_Desc_002</x:t>
@@ -57,274 +228,118 @@
     <x:t>Term006_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
+    <x:t>Cocruwa002_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa001_Desc_002</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa007_Desc_002</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
+    <x:t>Encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>EncyclopediaEnum</x:t>
+    <x:t>Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
     <x:t>Term</x:t>
   </x:si>
   <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Desc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
     <x:t>Array</x:t>
   </x:si>
   <x:si>
-    <x:t>Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_015</x:t>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa_020</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa_023</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa_011</x:t>
   </x:si>
   <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
+    <x:t>Cocruwa006_Title</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa010_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa006_Title</x:t>
+    <x:t>Term_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_008</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1089,7 +1104,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:K38"/>
+  <x:dimension ref="A1:K44"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1101,45 +1116,45 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F1" s="7"/>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F2" s="7"/>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1150,7 +1165,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1164,16 +1179,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F5" s="7"/>
       <x:c r="G5" s="1"/>
@@ -1184,16 +1199,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>83</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K6" s="1"/>
     </x:row>
@@ -1202,16 +1217,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>84</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="7"/>
       <x:c r="K7" s="2"/>
@@ -1221,16 +1236,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>84</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F8" s="8"/>
       <x:c r="K8" s="3"/>
@@ -1240,16 +1255,16 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>19</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F9" s="7"/>
       <x:c r="K9" s="2"/>
@@ -1259,16 +1274,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>90</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F10" s="8"/>
       <x:c r="K10" s="3"/>
@@ -1278,16 +1293,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>92</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F11" s="7"/>
       <x:c r="K11" s="1"/>
@@ -1297,16 +1312,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="7"/>
       <x:c r="K12" s="2"/>
@@ -1316,16 +1331,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>91</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>32</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F13" s="7"/>
       <x:c r="K13" s="2"/>
@@ -1335,16 +1350,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>91</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F14" s="7"/>
       <x:c r="K14" s="1"/>
@@ -1354,16 +1369,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>99</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F15" s="8"/>
       <x:c r="K15" s="1"/>
@@ -1373,16 +1388,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D16" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D16" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="E16" s="4" t="s">
-        <x:v>20</x:v>
       </x:c>
       <x:c r="F16" s="7"/>
       <x:c r="K16" s="2"/>
@@ -1392,16 +1407,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>93</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F17" s="8"/>
       <x:c r="K17" s="2"/>
@@ -1411,16 +1426,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>93</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>26</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F18" s="7"/>
       <x:c r="K18" s="2"/>
@@ -1430,16 +1445,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F19" s="8"/>
       <x:c r="K19" s="2"/>
@@ -1449,16 +1464,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>100</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E20" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F20" s="7"/>
       <x:c r="K20" s="5"/>
@@ -1468,16 +1483,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>97</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F21" s="8"/>
       <x:c r="K21" s="1"/>
@@ -1487,16 +1502,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>97</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F22" s="7"/>
       <x:c r="K22" s="2"/>
@@ -1506,16 +1521,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F23" s="8"/>
       <x:c r="K23" s="2"/>
@@ -1525,16 +1540,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>1</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F24" s="7"/>
       <x:c r="K24" s="2"/>
@@ -1544,16 +1559,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F25" s="8"/>
       <x:c r="K25" s="2"/>
@@ -1563,16 +1578,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E26" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F26" s="7"/>
       <x:c r="K26" s="5"/>
@@ -1582,16 +1597,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F27" s="8"/>
       <x:c r="K27" s="1"/>
@@ -1601,16 +1616,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>74</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>87</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="K28" s="2"/>
     </x:row>
@@ -1619,16 +1634,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>70</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K29" s="2"/>
     </x:row>
@@ -1637,16 +1652,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>72</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K30" s="2"/>
     </x:row>
@@ -1655,16 +1670,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>71</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="E31" t="s">
-        <x:v>6</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K31" s="2"/>
     </x:row>
@@ -1673,16 +1688,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>75</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="K32" s="2"/>
     </x:row>
@@ -1691,16 +1706,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>73</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>37</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>11</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K33" s="2"/>
     </x:row>
@@ -1709,16 +1724,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>78</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K34" s="2"/>
     </x:row>
@@ -1727,16 +1742,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>13</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="K35" s="2"/>
     </x:row>
@@ -1745,16 +1760,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>69</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="K36" s="2"/>
     </x:row>
@@ -1763,21 +1778,62 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>39</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K37" s="2"/>
     </x:row>
-    <x:row r="38" spans="11:11">
+    <x:row r="38" spans="1:11">
+      <x:c r="A38">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B38" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D38" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E38" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K38" s="2"/>
+    </x:row>
+    <x:row r="39" spans="1:5">
+      <x:c r="A39">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B39" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C39" s="2" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D39" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E39" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="3:3">
+      <x:c r="C42" s="2"/>
+    </x:row>
+    <x:row r="43" spans="3:3">
+      <x:c r="C43" s="2"/>
+    </x:row>
+    <x:row r="44" spans="3:3">
+      <x:c r="C44" s="2"/>
     </x:row>
   </x:sheetData>
   <x:sortState columnSort="0" caseSensitive="0" ref="D6:E30">

--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -19,7 +19,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="107">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="111">
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
   <x:si>
     <x:t>Term007_Desc_002</x:t>
   </x:si>
@@ -27,103 +48,238 @@
     <x:t>Term007_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa009_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa001_Title</x:t>
   </x:si>
   <x:si>
     <x:t>EncyclopediaEnum</x:t>
   </x:si>
   <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa002_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa011_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Order</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
   </x:si>
   <x:si>
     <x:t>Term007_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_006</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa_017</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa_006</x:t>
+    <x:t>Cocruwa_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa_013</x:t>
@@ -132,214 +288,70 @@
     <x:t>Cocruwa_010</x:t>
   </x:si>
   <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_005</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa_003</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa_016</x:t>
+    <x:t>Cocruwa_012</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa_021</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_012</x:t>
-  </x:si>
-  <x:si>
     <x:t>History_002</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa_014</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa_015</x:t>
-  </x:si>
-  <x:si>
     <x:t>History_004</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
+    <x:t>Term_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_011</x:t>
   </x:si>
   <x:si>
     <x:t>Title</x:t>
   </x:si>
   <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Desc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
+    <x:t>Term</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa</x:t>
   </x:si>
   <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_008</x:t>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1116,45 +1128,49 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F1" s="7"/>
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F1" s="7" t="s">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F2" s="7"/>
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="F2" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1165,7 +1181,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1179,18 +1195,20 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F5" s="7"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="G5" s="1"/>
       <x:c r="K5" s="1"/>
     </x:row>
@@ -1199,16 +1217,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>5</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="s">
+        <x:v>110</x:v>
       </x:c>
       <x:c r="K6" s="1"/>
     </x:row>
@@ -1217,18 +1238,20 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F7" s="7"/>
+      <x:c r="F7" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -1236,18 +1259,20 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="F8" s="8"/>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:11">
@@ -1255,18 +1280,20 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>11</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F9" s="7"/>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K9" s="2"/>
     </x:row>
     <x:row r="10" spans="1:11">
@@ -1274,18 +1301,20 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F10" s="8"/>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1293,18 +1322,20 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F11" s="7"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F11" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K11" s="1"/>
     </x:row>
     <x:row r="12" spans="1:11">
@@ -1312,18 +1343,20 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>103</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="7"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F12" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K12" s="2"/>
     </x:row>
     <x:row r="13" spans="1:11">
@@ -1331,18 +1364,20 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F13" s="7"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F13" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K13" s="2"/>
     </x:row>
     <x:row r="14" spans="1:11">
@@ -1350,18 +1385,20 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="F14" s="7"/>
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F14" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K14" s="1"/>
     </x:row>
     <x:row r="15" spans="1:11">
@@ -1369,18 +1406,20 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F15" s="8"/>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F15" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K15" s="1"/>
     </x:row>
     <x:row r="16" spans="1:11">
@@ -1388,18 +1427,20 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F16" s="7"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F16" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K16" s="2"/>
     </x:row>
     <x:row r="17" spans="1:11">
@@ -1407,18 +1448,20 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F17" s="8"/>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K17" s="2"/>
     </x:row>
     <x:row r="18" spans="1:11">
@@ -1426,18 +1469,20 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="F18" s="7"/>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F18" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K18" s="2"/>
     </x:row>
     <x:row r="19" spans="1:11">
@@ -1445,18 +1490,20 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D19" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F19" s="8"/>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K19" s="2"/>
     </x:row>
     <x:row r="20" spans="1:11">
@@ -1464,18 +1511,20 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>104</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E20" s="5" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F20" s="7"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F20" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K20" s="5"/>
     </x:row>
     <x:row r="21" spans="1:11">
@@ -1483,18 +1532,20 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F21" s="8"/>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F21" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K21" s="1"/>
     </x:row>
     <x:row r="22" spans="1:11">
@@ -1502,18 +1553,20 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E22" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F22" s="7"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F22" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K22" s="2"/>
     </x:row>
     <x:row r="23" spans="1:11">
@@ -1521,18 +1574,20 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F23" s="8"/>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F23" s="8" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K23" s="2"/>
     </x:row>
     <x:row r="24" spans="1:11">
@@ -1540,18 +1595,20 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F24" s="7"/>
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F24" s="7" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K24" s="2"/>
     </x:row>
     <x:row r="25" spans="1:11">
@@ -1559,18 +1616,20 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F25" s="8"/>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="F25" s="8" t="s">
+        <x:v>109</x:v>
+      </x:c>
       <x:c r="K25" s="2"/>
     </x:row>
     <x:row r="26" spans="1:11">
@@ -1578,18 +1637,20 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E26" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F26" s="7"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F26" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="K26" s="5"/>
     </x:row>
     <x:row r="27" spans="1:11">
@@ -1597,18 +1658,20 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F27" s="8"/>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F27" s="8" t="s">
+        <x:v>110</x:v>
+      </x:c>
       <x:c r="K27" s="1"/>
     </x:row>
     <x:row r="28" spans="1:11">
@@ -1616,16 +1679,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>99</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K28" s="2"/>
     </x:row>
@@ -1634,16 +1700,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>91</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K29" s="2"/>
     </x:row>
@@ -1652,16 +1721,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>94</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K30" s="2"/>
     </x:row>
@@ -1670,16 +1742,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>92</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E31" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K31" s="2"/>
     </x:row>
@@ -1688,16 +1763,19 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>93</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K32" s="2"/>
     </x:row>
@@ -1706,16 +1784,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>98</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>68</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K33" s="2"/>
     </x:row>
@@ -1724,16 +1805,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
-        <x:v>95</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>56</x:v>
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K34" s="2"/>
     </x:row>
@@ -1742,16 +1826,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>44</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>60</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K35" s="2"/>
     </x:row>
@@ -1760,16 +1847,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>96</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>55</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K36" s="2"/>
     </x:row>
@@ -1778,16 +1868,19 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>47</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>84</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>58</x:v>
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K37" s="2"/>
     </x:row>
@@ -1796,34 +1889,40 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C38" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D38" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E38" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="s">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K38" s="2"/>
     </x:row>
-    <x:row r="39" spans="1:5">
+    <x:row r="39" spans="1:6">
       <x:c r="A39">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="s">
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="3:3">

--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -19,339 +19,354 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="111">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="116">
+  <x:si>
+    <x:t>Cocruwa009_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Encyclopedia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocruwa005_Title</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
     <x:t>History001_Title</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa007_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
     <x:t>History002_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocruwa007_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>Term007_Desc_002</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>Term007_Desc_001</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
     <x:t>History003_Title</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EncyclopediaEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocruwa005_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EncyclopediaEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_001</x:t>
+    <x:t>Cocruwa_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
   </x:si>
   <x:si>
     <x:t>Order</x:t>
   </x:si>
   <x:si>
-    <x:t>Term003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Encyclopedia</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Desc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1128,49 +1143,49 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F1" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F2" s="7" t="s">
-        <x:v>53</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1181,7 +1196,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1195,19 +1210,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G5" s="1"/>
       <x:c r="K5" s="1"/>
@@ -1217,19 +1232,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D6" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="F6" s="6" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="1"/>
     </x:row>
@@ -1238,19 +1253,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F7" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K7" s="2"/>
     </x:row>
@@ -1259,19 +1274,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>35</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K8" s="3"/>
     </x:row>
@@ -1280,19 +1295,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D9" t="s">
-        <x:v>3</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F9" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K9" s="2"/>
     </x:row>
@@ -1301,19 +1316,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>5</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
@@ -1322,19 +1337,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="D11" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="F11" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K11" s="1"/>
     </x:row>
@@ -1343,19 +1358,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>50</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F12" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="2"/>
     </x:row>
@@ -1364,19 +1379,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>2</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>6</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F13" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K13" s="2"/>
     </x:row>
@@ -1385,19 +1400,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>2</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F14" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K14" s="1"/>
     </x:row>
@@ -1406,19 +1421,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F15" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K15" s="1"/>
     </x:row>
@@ -1430,16 +1445,16 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F16" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K16" s="2"/>
     </x:row>
@@ -1448,19 +1463,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K17" s="2"/>
     </x:row>
@@ -1469,19 +1484,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K18" s="2"/>
     </x:row>
@@ -1490,19 +1505,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D19" t="s">
-        <x:v>46</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K19" s="2"/>
     </x:row>
@@ -1511,19 +1526,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>46</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E20" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F20" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K20" s="5"/>
     </x:row>
@@ -1532,19 +1547,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K21" s="1"/>
     </x:row>
@@ -1553,19 +1568,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>41</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E22" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F22" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K22" s="2"/>
     </x:row>
@@ -1574,19 +1589,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K23" s="2"/>
     </x:row>
@@ -1595,19 +1610,19 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>45</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F24" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K24" s="2"/>
     </x:row>
@@ -1616,19 +1631,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F25" s="8" t="s">
-        <x:v>109</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="K25" s="2"/>
     </x:row>
@@ -1637,19 +1652,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>39</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E26" s="5" t="s">
-        <x:v>43</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F26" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K26" s="5"/>
     </x:row>
@@ -1658,19 +1673,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>39</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F27" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="K27" s="1"/>
     </x:row>
@@ -1679,19 +1694,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>70</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F28" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K28" s="2"/>
     </x:row>
@@ -1700,19 +1715,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>71</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F29" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K29" s="2"/>
     </x:row>
@@ -1721,19 +1736,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>72</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F30" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K30" s="2"/>
     </x:row>
@@ -1742,19 +1757,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E31" t="s">
-        <x:v>19</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F31" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K31" s="2"/>
     </x:row>
@@ -1763,19 +1778,19 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>29</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F32" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K32" s="2"/>
     </x:row>
@@ -1784,19 +1799,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F33" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K33" s="2"/>
     </x:row>
@@ -1808,16 +1823,16 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="C34" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F34" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K34" s="2"/>
     </x:row>
@@ -1826,19 +1841,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>92</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F35" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K35" s="2"/>
     </x:row>
@@ -1847,19 +1862,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>33</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F36" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K36" s="2"/>
     </x:row>
@@ -1868,19 +1883,19 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>94</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>101</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>40</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F37" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K37" s="2"/>
     </x:row>
@@ -1889,19 +1904,19 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C38" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D38" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E38" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F38" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="K38" s="2"/>
     </x:row>
@@ -1910,23 +1925,64 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F39" s="6" t="s">
-        <x:v>110</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="3:3">
-      <x:c r="C42" s="2"/>
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:6">
+      <x:c r="A40">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D40" s="2" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E40" s="5" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:6">
+      <x:c r="A41">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D41" s="2" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="2:3">
+      <x:c r="B42" s="1"/>
+      <x:c r="C42" s="1"/>
     </x:row>
     <x:row r="43" spans="3:3">
       <x:c r="C43" s="2"/>

--- a/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
+++ b/morpg/morpg/Assets/TableData/Table_Encyclopedia.xlsx
@@ -19,111 +19,348 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="116">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="131">
+  <x:si>
+    <x:t>Character004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Title</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocruwa009_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa006_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa011_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Desc_001</x:t>
+    <x:t>Character001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_023</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_022</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_016</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_019</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodeName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_017</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa_025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Index</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Array</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Desc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Order</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa010_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa001_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term004_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term006_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa012_Title</x:t>
   </x:si>
   <x:si>
     <x:t>Cocruwa004_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa010_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa012_Title</x:t>
+    <x:t>History001_Title</x:t>
   </x:si>
   <x:si>
     <x:t>Term001_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa001_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term004_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Desc_001</x:t>
+    <x:t>Cocruwa008_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa013_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>History003_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa008_Desc_001</x:t>
+    <x:t>Cocruwa010_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa008_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa005_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa011_Desc_002</x:t>
   </x:si>
   <x:si>
     <x:t>Term002_Desc_001</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocruwa011_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa013_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa010_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa008_Title</x:t>
+    <x:t>Cocruwa005_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa003_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa014_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EncyclopediaEnum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa009_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>History002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa002_Desc_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term007_Desc_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocruwa006_Desc_001</x:t>
   </x:si>
   <x:si>
     <x:t>Term004_Title</x:t>
@@ -132,6 +369,9 @@
     <x:t>Encyclopedia</x:t>
   </x:si>
   <x:si>
+    <x:t>Term007_Title</x:t>
+  </x:si>
+  <x:si>
     <x:t>Term003_Title</x:t>
   </x:si>
   <x:si>
@@ -144,229 +384,34 @@
     <x:t>Term001_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>Term007_Title</x:t>
-  </x:si>
-  <x:si>
     <x:t>Term005_Title</x:t>
   </x:si>
   <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History004_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History001_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History002_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa006_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term007_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa002_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History003_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa003_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EncyclopediaEnum</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa009_Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa005_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_020</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_018</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_022</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_016</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_006</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_017</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CodeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_010</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Term</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Title</x:t>
-  </x:si>
-  <x:si>
-    <x:t>History</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Desc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Array</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Index</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Order</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Desc_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_024</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa_025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocruwa014_Title</x:t>
+    <x:t>Character001_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character002_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character004_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character003_Title</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Character_001</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1131,7 +1176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:K44"/>
+  <x:dimension ref="A1:K46"/>
   <x:sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="8.796875" bestFit="1" customWidth="1"/>
@@ -1143,49 +1188,49 @@
   <x:sheetData>
     <x:row r="1" spans="1:7">
       <x:c r="A1" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F1" s="7" t="s">
-        <x:v>46</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F2" s="7" t="s">
-        <x:v>110</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1196,7 +1241,7 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1210,19 +1255,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G5" s="1"/>
       <x:c r="K5" s="1"/>
@@ -1232,19 +1277,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D6" t="s">
-        <x:v>50</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K6" s="1"/>
     </x:row>
@@ -1253,19 +1298,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D7" t="s">
-        <x:v>24</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>59</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F7" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K7" s="2"/>
     </x:row>
@@ -1274,19 +1319,19 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D8" t="s">
-        <x:v>24</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="3"/>
     </x:row>
@@ -1295,19 +1340,19 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E9" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="D9" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E9" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="F9" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K9" s="2"/>
     </x:row>
@@ -1316,19 +1361,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>48</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F10" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
@@ -1337,19 +1382,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>47</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F11" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K11" s="1"/>
     </x:row>
@@ -1358,19 +1403,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>57</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F12" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K12" s="2"/>
     </x:row>
@@ -1379,19 +1424,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>53</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>55</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F13" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K13" s="2"/>
     </x:row>
@@ -1400,19 +1445,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>53</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F14" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K14" s="1"/>
     </x:row>
@@ -1421,19 +1466,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D15" t="s">
-        <x:v>34</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F15" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K15" s="1"/>
     </x:row>
@@ -1442,19 +1487,19 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D16" t="s">
-        <x:v>34</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E16" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F16" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K16" s="2"/>
     </x:row>
@@ -1463,19 +1508,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D17" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K17" s="2"/>
     </x:row>
@@ -1484,19 +1529,19 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D18" t="s">
-        <x:v>63</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E18" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F18" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K18" s="2"/>
     </x:row>
@@ -1505,19 +1550,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D19" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="D19" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E19" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F19" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K19" s="2"/>
     </x:row>
@@ -1526,19 +1571,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D20" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E20" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F20" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K20" s="5"/>
     </x:row>
@@ -1547,19 +1592,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D21" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F21" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K21" s="1"/>
     </x:row>
@@ -1568,19 +1613,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D22" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E22" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F22" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K22" s="2"/>
     </x:row>
@@ -1589,19 +1634,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D23" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F23" s="8" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K23" s="2"/>
     </x:row>
@@ -1610,19 +1655,19 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D24" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E24" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="7" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K24" s="2"/>
     </x:row>
@@ -1631,19 +1676,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D25" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F25" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K25" s="2"/>
     </x:row>
@@ -1652,19 +1697,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D26" t="s">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E26" s="5" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F26" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K26" s="5"/>
     </x:row>
@@ -1673,19 +1718,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D27" t="s">
-        <x:v>3</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F27" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K27" s="1"/>
     </x:row>
@@ -1694,19 +1739,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B28" t="s">
-        <x:v>80</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E28" t="s">
-        <x:v>22</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F28" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K28" s="2"/>
     </x:row>
@@ -1715,19 +1760,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B29" t="s">
-        <x:v>85</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C29" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D29" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E29" t="s">
-        <x:v>30</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F29" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K29" s="2"/>
     </x:row>
@@ -1736,19 +1781,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B30" t="s">
-        <x:v>82</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C30" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D30" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E30" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K30" s="2"/>
     </x:row>
@@ -1757,19 +1802,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B31" t="s">
-        <x:v>81</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C31" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D31" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E31" t="s">
-        <x:v>25</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F31" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K31" s="2"/>
     </x:row>
@@ -1778,19 +1823,19 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B32" t="s">
-        <x:v>74</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C32" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D32" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E32" t="s">
-        <x:v>15</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F32" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K32" s="2"/>
     </x:row>
@@ -1799,19 +1844,19 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B33" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D33" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E33" t="s">
-        <x:v>26</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F33" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K33" s="2"/>
     </x:row>
@@ -1820,19 +1865,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B34" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C34" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C34" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="D34" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E34" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F34" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K34" s="2"/>
     </x:row>
@@ -1841,19 +1886,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B35" t="s">
-        <x:v>100</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C35" t="s">
-        <x:v>104</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D35" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E35" t="s">
-        <x:v>27</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F35" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K35" s="2"/>
     </x:row>
@@ -1862,19 +1907,19 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B36" t="s">
-        <x:v>77</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C36" t="s">
-        <x:v>104</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D36" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E36" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F36" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K36" s="2"/>
     </x:row>
@@ -1883,19 +1928,19 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B37" t="s">
-        <x:v>71</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C37" t="s">
-        <x:v>104</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D37" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E37" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F37" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K37" s="2"/>
     </x:row>
@@ -1904,19 +1949,19 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C38" s="2" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C38" s="2" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="D38" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E38" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F38" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K38" s="2"/>
     </x:row>
@@ -1925,19 +1970,19 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B39" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C39" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D39" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E39" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F39" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:6">
@@ -1945,19 +1990,19 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D40" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E40" s="5" t="s">
-        <x:v>111</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F40" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:6">
@@ -1965,30 +2010,120 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D41" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F41" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:6">
+      <x:c r="A42">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D42" s="2" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E42" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:6">
+      <x:c r="A43">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D43" s="2" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E43" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:6">
+      <x:c r="A44">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D44" s="2" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E44" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:6">
+      <x:c r="A45">
         <x:v>44</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42" spans="2:3">
-      <x:c r="B42" s="1"/>
-      <x:c r="C42" s="1"/>
-    </x:row>
-    <x:row r="43" spans="3:3">
-      <x:c r="C43" s="2"/>
-    </x:row>
-    <x:row r="44" spans="3:3">
-      <x:c r="C44" s="2"/>
+      <x:c r="B45" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D45" s="2" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="E45" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:6">
+      <x:c r="A46">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D46" s="2" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E46" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:sortState columnSort="0" caseSensitive="0" ref="D6:E30">
